--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,10 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
@@ -460,22 +455,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.63335</v>
+        <v>16.79849</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70425</v>
+        <v>16.17701</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2237</v>
+        <v>16.20246</v>
       </c>
       <c r="F2" t="n">
-        <v>21.56887</v>
+        <v>21.56401</v>
       </c>
       <c r="G2" t="n">
-        <v>21.74356</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.91587</v>
+        <v>33.4091</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.62596</v>
+        <v>16.65996</v>
       </c>
       <c r="D3" t="n">
-        <v>15.86097</v>
+        <v>15.62263</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2628</v>
+        <v>16.31688</v>
       </c>
       <c r="F3" t="n">
-        <v>21.71092</v>
+        <v>21.77702</v>
       </c>
       <c r="G3" t="n">
-        <v>21.66608</v>
-      </c>
-      <c r="H3" t="n">
-        <v>34.10842</v>
+        <v>34.44319</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.53623</v>
+        <v>16.77858</v>
       </c>
       <c r="D4" t="n">
-        <v>15.73889</v>
+        <v>16.09437</v>
       </c>
       <c r="E4" t="n">
-        <v>16.49517</v>
+        <v>16.58264</v>
       </c>
       <c r="F4" t="n">
-        <v>22.00175</v>
+        <v>21.66386</v>
       </c>
       <c r="G4" t="n">
-        <v>21.66055</v>
-      </c>
-      <c r="H4" t="n">
-        <v>33.72266</v>
+        <v>33.90799</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.6687</v>
+        <v>16.58697</v>
       </c>
       <c r="D5" t="n">
-        <v>16.18017</v>
+        <v>16.05784</v>
       </c>
       <c r="E5" t="n">
-        <v>16.47534</v>
+        <v>16.31195</v>
       </c>
       <c r="F5" t="n">
-        <v>21.60535</v>
+        <v>21.40776</v>
       </c>
       <c r="G5" t="n">
-        <v>22.11096</v>
-      </c>
-      <c r="H5" t="n">
-        <v>33.86195</v>
+        <v>34.61185</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.55208</v>
+        <v>16.62036</v>
       </c>
       <c r="D6" t="n">
-        <v>15.42279</v>
+        <v>15.93635</v>
       </c>
       <c r="E6" t="n">
-        <v>16.00958</v>
+        <v>16.10602</v>
       </c>
       <c r="F6" t="n">
-        <v>22.14999</v>
+        <v>21.67667</v>
       </c>
       <c r="G6" t="n">
-        <v>21.42687</v>
-      </c>
-      <c r="H6" t="n">
-        <v>34.40276</v>
+        <v>33.54371</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.43706</v>
+        <v>16.32974</v>
       </c>
       <c r="D7" t="n">
-        <v>15.93868</v>
+        <v>15.89244</v>
       </c>
       <c r="E7" t="n">
-        <v>16.23733</v>
+        <v>16.22252</v>
       </c>
       <c r="F7" t="n">
-        <v>22.0102</v>
+        <v>21.26406</v>
       </c>
       <c r="G7" t="n">
-        <v>21.61736</v>
-      </c>
-      <c r="H7" t="n">
-        <v>33.98859</v>
+        <v>33.91115</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40704</v>
+        <v>16.66378</v>
       </c>
       <c r="D8" t="n">
-        <v>15.5228</v>
+        <v>16.08323</v>
       </c>
       <c r="E8" t="n">
-        <v>16.19831</v>
+        <v>16.40135</v>
       </c>
       <c r="F8" t="n">
-        <v>22.02098</v>
+        <v>21.66441</v>
       </c>
       <c r="G8" t="n">
-        <v>21.86203</v>
-      </c>
-      <c r="H8" t="n">
-        <v>33.93794</v>
+        <v>34.80353</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.44145</v>
+        <v>16.49751</v>
       </c>
       <c r="D9" t="n">
-        <v>15.48256</v>
+        <v>15.71066</v>
       </c>
       <c r="E9" t="n">
-        <v>16.64972</v>
+        <v>16.0497</v>
       </c>
       <c r="F9" t="n">
-        <v>21.21289</v>
+        <v>21.54711</v>
       </c>
       <c r="G9" t="n">
-        <v>21.59108</v>
-      </c>
-      <c r="H9" t="n">
-        <v>33.85393</v>
+        <v>34.22825</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +631,281 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.64361</v>
+        <v>16.85009</v>
       </c>
       <c r="D10" t="n">
-        <v>16.07962</v>
+        <v>15.96905</v>
       </c>
       <c r="E10" t="n">
-        <v>16.42858</v>
+        <v>16.17962</v>
       </c>
       <c r="F10" t="n">
-        <v>21.44811</v>
+        <v>21.44314</v>
       </c>
       <c r="G10" t="n">
-        <v>22.22716</v>
-      </c>
-      <c r="H10" t="n">
-        <v>33.97513</v>
+        <v>33.33458</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.84735</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.44301</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.66564</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.4296</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.82159</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16.58465</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.50567</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.5501</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.8254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>16.97825</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.27617</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.53828</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.56109</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.84669</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>16.62628</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.39369</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.547</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.00857</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.78744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16.9361</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.1486</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.43437</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.56325</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.80071</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16.78757</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.53323</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.54658</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.04907</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.79427</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17.02368</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.22286</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.51576</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.29278</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.04934</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.81846</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16.58972</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.25206</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.54635</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.39211</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.79824</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.91898</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.5236</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.66822</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.10475</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.86089</v>
       </c>
     </row>
   </sheetData>
